--- a/config/sort_game_basic_card_config.xlsx
+++ b/config/sort_game_basic_card_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12860"/>
+    <workbookView windowHeight="23960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4301,7 +4301,7 @@
     <t>KENNEDY_WORD_LEADER_196</t>
   </si>
   <si>
-    <t>Kennedy</t>
+    <t>Washington</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_KENNEDY</t>
@@ -4310,7 +4310,7 @@
     <t>CLINTON_WORD_LEADER_196</t>
   </si>
   <si>
-    <t>Clinton</t>
+    <t>Jefferson</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_CLINTON</t>
@@ -4328,7 +4328,7 @@
     <t>REAGAN_WORD_LEADER_196</t>
   </si>
   <si>
-    <t>Reagan</t>
+    <t>Roosevelt</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_REAGAN</t>
@@ -4337,7 +4337,7 @@
     <t>BUSH_WORD_LEADER_196</t>
   </si>
   <si>
-    <t>Bush</t>
+    <t>Wilson</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_BUSH</t>
@@ -4346,7 +4346,7 @@
     <t>OBAMA_WORD_LEADER_196</t>
   </si>
   <si>
-    <t>Obama</t>
+    <t>Jackson</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_OBAMA</t>
@@ -4364,7 +4364,7 @@
     <t>BIDEN_WORD_LEADER_196</t>
   </si>
   <si>
-    <t>Biden</t>
+    <t>Madison</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_BIDEN</t>
@@ -7985,7 +7985,7 @@
     <t>SYBARITE_WORD_FOODIE_726</t>
   </si>
   <si>
-    <t>Sybarite</t>
+    <t>Cuisine</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_SYBARITE</t>
@@ -7994,7 +7994,7 @@
     <t>HEDONISM_WORD_FOODIE_726</t>
   </si>
   <si>
-    <t>Hedonism</t>
+    <t>Savory</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_HEDONISM</t>
@@ -8003,7 +8003,7 @@
     <t>DISHES_WORD_FOODIE_726</t>
   </si>
   <si>
-    <t>Dishes</t>
+    <t>Delicacy</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_DISHES</t>
@@ -21497,7 +21497,7 @@
       <c r="A477" s="4" t="s">
         <v>1423</v>
       </c>
-      <c r="B477" s="4" t="s">
+      <c r="B477" s="6" t="s">
         <v>1424</v>
       </c>
       <c r="C477" s="4" t="s">
@@ -21510,7 +21510,7 @@
       <c r="A478" s="4" t="s">
         <v>1426</v>
       </c>
-      <c r="B478" s="4" t="s">
+      <c r="B478" s="6" t="s">
         <v>1427</v>
       </c>
       <c r="C478" s="4" t="s">
@@ -21536,7 +21536,7 @@
       <c r="A480" s="4" t="s">
         <v>1432</v>
       </c>
-      <c r="B480" s="4" t="s">
+      <c r="B480" s="6" t="s">
         <v>1433</v>
       </c>
       <c r="C480" s="4" t="s">
@@ -21549,7 +21549,7 @@
       <c r="A481" s="4" t="s">
         <v>1435</v>
       </c>
-      <c r="B481" s="4" t="s">
+      <c r="B481" s="6" t="s">
         <v>1436</v>
       </c>
       <c r="C481" s="4" t="s">
@@ -21562,7 +21562,7 @@
       <c r="A482" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B482" s="4" t="s">
+      <c r="B482" s="6" t="s">
         <v>1439</v>
       </c>
       <c r="C482" s="4" t="s">
@@ -21588,7 +21588,7 @@
       <c r="A484" s="4" t="s">
         <v>1444</v>
       </c>
-      <c r="B484" s="4" t="s">
+      <c r="B484" s="6" t="s">
         <v>1445</v>
       </c>
       <c r="C484" s="4" t="s">
@@ -26761,7 +26761,7 @@
       <c r="A898" s="4" t="s">
         <v>2651</v>
       </c>
-      <c r="B898" s="4" t="s">
+      <c r="B898" s="6" t="s">
         <v>2652</v>
       </c>
       <c r="C898" s="4" t="s">
@@ -26773,7 +26773,7 @@
       <c r="A899" s="4" t="s">
         <v>2654</v>
       </c>
-      <c r="B899" s="4" t="s">
+      <c r="B899" s="6" t="s">
         <v>2655</v>
       </c>
       <c r="C899" s="4" t="s">
@@ -26785,7 +26785,7 @@
       <c r="A900" s="4" t="s">
         <v>2657</v>
       </c>
-      <c r="B900" s="4" t="s">
+      <c r="B900" s="6" t="s">
         <v>2658</v>
       </c>
       <c r="C900" s="4" t="s">
